--- a/artfynd/A 31212-2025 artfynd.xlsx
+++ b/artfynd/A 31212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95981707</v>
+        <v>135221214</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullen, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555429</v>
+        <v>555441</v>
       </c>
       <c r="R2" t="n">
-        <v>6943509</v>
+        <v>6943488</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,64 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104442994</v>
+        <v>135221195</v>
       </c>
       <c r="B3" t="n">
-        <v>91966</v>
+        <v>91924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5321</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullen, N om, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555449</v>
+        <v>555330</v>
       </c>
       <c r="R3" t="n">
-        <v>6943460</v>
+        <v>6943509</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -841,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -855,46 +871,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>gammal grannaturskog i nordsluttning</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # nerfallna grovgrenar av urgamla aspar</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95981706</v>
+        <v>135221181</v>
       </c>
       <c r="B4" t="n">
-        <v>83307</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kullen, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555437</v>
+        <v>555223</v>
       </c>
       <c r="R4" t="n">
-        <v>6943445</v>
+        <v>6943496</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,12 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,64 +984,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104442995</v>
+        <v>95981707</v>
       </c>
       <c r="B5" t="n">
-        <v>80392</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kullen, N om, Mpd</t>
+          <t>Kullen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555449</v>
+        <v>555429</v>
       </c>
       <c r="R5" t="n">
-        <v>6943460</v>
+        <v>6943509</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,12 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,36 +1077,4909 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>gammal grannaturskog i nordsluttning, mot sydvänd hyggeskant</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>2 substratenheter # urgamla aspar, uppskattningsvis runt 300 år, mycket grovbarkiga, 6 cm höga barkåsar</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135221191</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>555298</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6943497</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135221210</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>555424</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6943510</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135221212</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>555436</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6943491</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135221213</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>555423</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6943489</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135221216</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>555453</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6943459</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135221221</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>555436</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6943512</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135221211</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>555442</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6943498</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104442994</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91966</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kullen, N om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>555449</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6943460</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>gammal grannaturskog i nordsluttning</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter # nerfallna grovgrenar av urgamla aspar</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135221208</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>555391</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6943515</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135221179</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>555255</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6943525</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135221180</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>555233</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6943506</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135221182</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>555232</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6943486</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135221184</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>555255</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6943491</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135221187</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>555287</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6943497</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135221188</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>555291</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6943507</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135221190</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>555276</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6943511</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135221203</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>555366</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6943491</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135221205</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>555382</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6943480</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135221220</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>555445</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6943509</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135221223</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>555413</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6943520</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135221224</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>555371</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6943530</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135221226</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>555352</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6943528</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>95981706</v>
+      </c>
+      <c r="B28" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kullen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>555437</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6943445</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135221207</v>
+      </c>
+      <c r="B29" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>555390</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6943516</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135221192</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>555299</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6943491</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135221197</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>555353</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6943492</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135221200</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>555364</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6943495</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135221217</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>555451</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6943454</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135221219</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>555460</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6943501</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135221189</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>555269</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6943521</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135221193</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>555307</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6943496</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135221225</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>555362</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6943529</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135221201</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>555364</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6943494</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135221198</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>555353</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6943492</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135221185</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>555257</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6943491</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135221199</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>555363</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6943498</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela stammen full.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135221209</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>555410</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6943513</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135221183</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>555234</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6943495</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135221194</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>555330</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6943504</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135221186</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>555278</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6943488</v>
+      </c>
+      <c r="S45" t="n">
+        <v>7</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>104442995</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kullen, N om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>555449</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6943460</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>gammal grannaturskog i nordsluttning, mot sydvänd hyggeskant</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>2 substratenheter # urgamla aspar, uppskattningsvis runt 300 år, mycket grovbarkiga, 6 cm höga barkåsar</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135221196</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>555341</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6943495</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135221202</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>555364</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6943494</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135221215</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>555450</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6943462</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135221218</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>555462</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6943501</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31212-2025 artfynd.xlsx
+++ b/artfynd/A 31212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1846,48 +1846,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104442994</v>
+        <v>135221204</v>
       </c>
       <c r="B13" t="n">
-        <v>91966</v>
+        <v>92153</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5321</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kullen, N om, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555449</v>
+        <v>555377</v>
       </c>
       <c r="R13" t="n">
-        <v>6943460</v>
+        <v>6943477</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1911,12 +1911,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,42 +1939,25 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>gammal grannaturskog i nordsluttning</t>
-        </is>
-      </c>
-      <c r="AN13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>1 substratenheter # nerfallna grovgrenar av urgamla aspar</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135221208</v>
+        <v>104442994</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>91966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,37 +1965,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>5321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öster-Skogsmyran, Mpd</t>
+          <t>Kullen, N om, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555391</v>
+        <v>555449</v>
       </c>
       <c r="R14" t="n">
-        <v>6943515</v>
+        <v>6943460</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2026,22 +2019,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2050,50 +2033,68 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>gammal grannaturskog i nordsluttning</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>1 substratenheter # nerfallna grovgrenar av urgamla aspar</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135221179</v>
+        <v>135221208</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,13 +2104,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555255</v>
+        <v>555391</v>
       </c>
       <c r="R15" t="n">
-        <v>6943525</v>
+        <v>6943515</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2138,7 +2139,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2148,7 +2149,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2175,7 +2176,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135221180</v>
+        <v>135221179</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2210,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555233</v>
+        <v>555255</v>
       </c>
       <c r="R16" t="n">
-        <v>6943506</v>
+        <v>6943525</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2245,7 +2246,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2255,7 +2256,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,7 +2283,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135221182</v>
+        <v>135221180</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2317,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555232</v>
+        <v>555233</v>
       </c>
       <c r="R17" t="n">
-        <v>6943486</v>
+        <v>6943506</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2352,7 +2353,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2363,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,7 +2390,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135221184</v>
+        <v>135221182</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2424,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555255</v>
+        <v>555232</v>
       </c>
       <c r="R18" t="n">
-        <v>6943491</v>
+        <v>6943486</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2459,7 +2460,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2469,7 +2470,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2496,7 +2497,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135221187</v>
+        <v>135221184</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2531,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555287</v>
+        <v>555255</v>
       </c>
       <c r="R19" t="n">
-        <v>6943497</v>
+        <v>6943491</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2566,7 +2567,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2576,7 +2577,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,7 +2604,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135221188</v>
+        <v>135221187</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2638,10 +2639,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555291</v>
+        <v>555287</v>
       </c>
       <c r="R20" t="n">
-        <v>6943507</v>
+        <v>6943497</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2673,7 +2674,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2683,7 +2684,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2710,7 +2711,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135221190</v>
+        <v>135221188</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2745,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555276</v>
+        <v>555291</v>
       </c>
       <c r="R21" t="n">
-        <v>6943511</v>
+        <v>6943507</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2780,7 +2781,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2790,7 +2791,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2817,7 +2818,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135221203</v>
+        <v>135221190</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2852,13 +2853,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555366</v>
+        <v>555276</v>
       </c>
       <c r="R22" t="n">
-        <v>6943491</v>
+        <v>6943511</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2887,7 +2888,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2897,7 +2898,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2924,7 +2925,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135221205</v>
+        <v>135221203</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2959,13 +2960,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555382</v>
+        <v>555366</v>
       </c>
       <c r="R23" t="n">
-        <v>6943480</v>
+        <v>6943491</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2994,7 +2995,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3004,7 +3005,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,7 +3032,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135221220</v>
+        <v>135221205</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3066,13 +3067,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555445</v>
+        <v>555382</v>
       </c>
       <c r="R24" t="n">
-        <v>6943509</v>
+        <v>6943480</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3101,7 +3102,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3111,7 +3112,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3138,7 +3139,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135221223</v>
+        <v>135221220</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3173,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555413</v>
+        <v>555445</v>
       </c>
       <c r="R25" t="n">
-        <v>6943520</v>
+        <v>6943509</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3208,7 +3209,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3218,7 +3219,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3245,7 +3246,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135221224</v>
+        <v>135221223</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3280,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555371</v>
+        <v>555413</v>
       </c>
       <c r="R26" t="n">
-        <v>6943530</v>
+        <v>6943520</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3315,7 +3316,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3325,7 +3326,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3352,7 +3353,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135221226</v>
+        <v>135221224</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3387,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555352</v>
+        <v>555371</v>
       </c>
       <c r="R27" t="n">
-        <v>6943528</v>
+        <v>6943530</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3422,7 +3423,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3432,7 +3433,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3459,48 +3460,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95981706</v>
+        <v>135221226</v>
       </c>
       <c r="B28" t="n">
-        <v>83307</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kullen, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555437</v>
+        <v>555352</v>
       </c>
       <c r="R28" t="n">
-        <v>6943445</v>
+        <v>6943528</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3524,12 +3525,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,26 +3555,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135221207</v>
+        <v>95981706</v>
       </c>
       <c r="B29" t="n">
-        <v>83358</v>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3591,17 +3598,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öster-Skogsmyran, Mpd</t>
+          <t>Kullen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555390</v>
+        <v>555437</v>
       </c>
       <c r="R29" t="n">
-        <v>6943516</v>
+        <v>6943445</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3625,22 +3632,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3655,22 +3652,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135221192</v>
+        <v>135221207</v>
       </c>
       <c r="B30" t="n">
-        <v>80488</v>
+        <v>83358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3678,21 +3679,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3702,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555299</v>
+        <v>555390</v>
       </c>
       <c r="R30" t="n">
-        <v>6943491</v>
+        <v>6943516</v>
       </c>
       <c r="S30" t="n">
         <v>6</v>
@@ -3737,7 +3738,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3747,7 +3748,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3774,7 +3775,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135221197</v>
+        <v>135221192</v>
       </c>
       <c r="B31" t="n">
         <v>80488</v>
@@ -3809,13 +3810,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555353</v>
+        <v>555299</v>
       </c>
       <c r="R31" t="n">
-        <v>6943492</v>
+        <v>6943491</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3844,7 +3845,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3854,7 +3855,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3881,7 +3882,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135221200</v>
+        <v>135221197</v>
       </c>
       <c r="B32" t="n">
         <v>80488</v>
@@ -3916,10 +3917,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555364</v>
+        <v>555353</v>
       </c>
       <c r="R32" t="n">
-        <v>6943495</v>
+        <v>6943492</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3951,7 +3952,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3961,7 +3962,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3988,7 +3989,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135221217</v>
+        <v>135221200</v>
       </c>
       <c r="B33" t="n">
         <v>80488</v>
@@ -4023,10 +4024,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555451</v>
+        <v>555364</v>
       </c>
       <c r="R33" t="n">
-        <v>6943454</v>
+        <v>6943495</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4058,7 +4059,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4068,7 +4069,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4095,7 +4096,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135221219</v>
+        <v>135221217</v>
       </c>
       <c r="B34" t="n">
         <v>80488</v>
@@ -4130,10 +4131,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555460</v>
+        <v>555451</v>
       </c>
       <c r="R34" t="n">
-        <v>6943501</v>
+        <v>6943454</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4165,7 +4166,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4175,7 +4176,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4202,32 +4203,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135221189</v>
+        <v>135221219</v>
       </c>
       <c r="B35" t="n">
-        <v>80492</v>
+        <v>80488</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4237,10 +4238,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555269</v>
+        <v>555460</v>
       </c>
       <c r="R35" t="n">
-        <v>6943521</v>
+        <v>6943501</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4272,7 +4273,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4282,7 +4283,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4309,7 +4310,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135221193</v>
+        <v>135221189</v>
       </c>
       <c r="B36" t="n">
         <v>80492</v>
@@ -4344,10 +4345,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555307</v>
+        <v>555269</v>
       </c>
       <c r="R36" t="n">
-        <v>6943496</v>
+        <v>6943521</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4379,7 +4380,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4389,7 +4390,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4416,7 +4417,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135221225</v>
+        <v>135221193</v>
       </c>
       <c r="B37" t="n">
         <v>80492</v>
@@ -4451,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555362</v>
+        <v>555307</v>
       </c>
       <c r="R37" t="n">
-        <v>6943529</v>
+        <v>6943496</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4486,7 +4487,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4496,7 +4497,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4523,10 +4524,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135221201</v>
+        <v>135221225</v>
       </c>
       <c r="B38" t="n">
-        <v>80493</v>
+        <v>80492</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4534,21 +4535,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4558,10 +4559,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555364</v>
+        <v>555362</v>
       </c>
       <c r="R38" t="n">
-        <v>6943494</v>
+        <v>6943529</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4593,7 +4594,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4603,7 +4604,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4630,10 +4631,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135221198</v>
+        <v>135221201</v>
       </c>
       <c r="B39" t="n">
-        <v>80499</v>
+        <v>80493</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4641,21 +4642,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4665,10 +4666,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555353</v>
+        <v>555364</v>
       </c>
       <c r="R39" t="n">
-        <v>6943492</v>
+        <v>6943494</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4700,7 +4701,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4710,7 +4711,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4737,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135221185</v>
+        <v>135221198</v>
       </c>
       <c r="B40" t="n">
-        <v>57972</v>
+        <v>80499</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,46 +4749,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555257</v>
+        <v>555353</v>
       </c>
       <c r="R40" t="n">
-        <v>6943491</v>
+        <v>6943492</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4819,7 +4808,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4829,7 +4818,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4856,27 +4845,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135221199</v>
+        <v>135221185</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4884,12 +4873,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4899,10 +4892,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555363</v>
+        <v>555257</v>
       </c>
       <c r="R41" t="n">
-        <v>6943498</v>
+        <v>6943491</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4934,7 +4927,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4944,12 +4937,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Hela stammen full.</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4976,7 +4964,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135221209</v>
+        <v>135221199</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -5009,7 +4997,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5019,13 +5007,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555410</v>
+        <v>555363</v>
       </c>
       <c r="R42" t="n">
-        <v>6943513</v>
+        <v>6943498</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5054,7 +5042,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5064,12 +5052,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall. Hela stammen full.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5096,10 +5084,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135221183</v>
+        <v>135221209</v>
       </c>
       <c r="B43" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5107,33 +5095,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5143,13 +5127,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555234</v>
+        <v>555410</v>
       </c>
       <c r="R43" t="n">
-        <v>6943495</v>
+        <v>6943513</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5178,7 +5162,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5188,7 +5172,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5215,44 +5204,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135221194</v>
+        <v>135221183</v>
       </c>
       <c r="B44" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5262,10 +5251,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555330</v>
+        <v>555234</v>
       </c>
       <c r="R44" t="n">
-        <v>6943504</v>
+        <v>6943495</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5297,7 +5286,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5307,7 +5296,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5334,48 +5323,60 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135221186</v>
+        <v>135221194</v>
       </c>
       <c r="B45" t="n">
-        <v>79131</v>
+        <v>58131</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>103023</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555278</v>
+        <v>555330</v>
       </c>
       <c r="R45" t="n">
-        <v>6943488</v>
+        <v>6943504</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5404,7 +5405,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5414,7 +5415,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5441,48 +5442,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104442995</v>
+        <v>135221186</v>
       </c>
       <c r="B46" t="n">
-        <v>80392</v>
+        <v>79131</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kullen, N om, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555449</v>
+        <v>555278</v>
       </c>
       <c r="R46" t="n">
-        <v>6943460</v>
+        <v>6943488</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5506,12 +5507,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5522,43 +5533,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>gammal grannaturskog i nordsluttning, mot sydvänd hyggeskant</t>
-        </is>
-      </c>
-      <c r="AN46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>2 substratenheter # urgamla aspar, uppskattningsvis runt 300 år, mycket grovbarkiga, 6 cm höga barkåsar</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135221196</v>
+        <v>104442995</v>
       </c>
       <c r="B47" t="n">
-        <v>80438</v>
+        <v>80392</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5586,17 +5580,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Öster-Skogsmyran, Mpd</t>
+          <t>Kullen, N om, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555341</v>
+        <v>555449</v>
       </c>
       <c r="R47" t="n">
-        <v>6943495</v>
+        <v>6943460</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5620,22 +5614,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5646,23 +5630,40 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>gammal grannaturskog i nordsluttning, mot sydvänd hyggeskant</t>
+        </is>
+      </c>
+      <c r="AN47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>2 substratenheter # urgamla aspar, uppskattningsvis runt 300 år, mycket grovbarkiga, 6 cm höga barkåsar</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135221202</v>
+        <v>135221196</v>
       </c>
       <c r="B48" t="n">
         <v>80438</v>
@@ -5697,13 +5698,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555364</v>
+        <v>555341</v>
       </c>
       <c r="R48" t="n">
-        <v>6943494</v>
+        <v>6943495</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5732,7 +5733,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5742,7 +5743,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5769,7 +5770,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135221215</v>
+        <v>135221202</v>
       </c>
       <c r="B49" t="n">
         <v>80438</v>
@@ -5804,10 +5805,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555450</v>
+        <v>555364</v>
       </c>
       <c r="R49" t="n">
-        <v>6943462</v>
+        <v>6943494</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5839,7 +5840,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5849,7 +5850,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,7 +5877,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135221218</v>
+        <v>135221215</v>
       </c>
       <c r="B50" t="n">
         <v>80438</v>
@@ -5911,10 +5912,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555462</v>
+        <v>555450</v>
       </c>
       <c r="R50" t="n">
-        <v>6943501</v>
+        <v>6943462</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5946,7 +5947,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5956,7 +5957,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5980,6 +5981,113 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135221218</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>555462</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6943501</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31212-2025 artfynd.xlsx
+++ b/artfynd/A 31212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135221181</v>
+        <v>95981707</v>
       </c>
       <c r="B4" t="n">
-        <v>79405</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster-Skogsmyran, Mpd</t>
+          <t>Kullen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555223</v>
+        <v>555429</v>
       </c>
       <c r="R4" t="n">
-        <v>6943496</v>
+        <v>6943509</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +974,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95981707</v>
+        <v>135221191</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,17 +1021,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kullen, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555429</v>
+        <v>555298</v>
       </c>
       <c r="R5" t="n">
-        <v>6943509</v>
+        <v>6943497</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,12 +1055,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,23 +1085,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135221191</v>
+        <v>135221210</v>
       </c>
       <c r="B6" t="n">
         <v>91974</v>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555298</v>
+        <v>555424</v>
       </c>
       <c r="R6" t="n">
-        <v>6943497</v>
+        <v>6943510</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135221210</v>
+        <v>135221212</v>
       </c>
       <c r="B7" t="n">
         <v>91974</v>
@@ -1239,13 +1239,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555424</v>
+        <v>555436</v>
       </c>
       <c r="R7" t="n">
-        <v>6943510</v>
+        <v>6943491</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135221212</v>
+        <v>135221213</v>
       </c>
       <c r="B8" t="n">
         <v>91974</v>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555436</v>
+        <v>555423</v>
       </c>
       <c r="R8" t="n">
-        <v>6943491</v>
+        <v>6943489</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135221213</v>
+        <v>135221216</v>
       </c>
       <c r="B9" t="n">
         <v>91974</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555423</v>
+        <v>555453</v>
       </c>
       <c r="R9" t="n">
-        <v>6943489</v>
+        <v>6943459</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135221216</v>
+        <v>135221221</v>
       </c>
       <c r="B10" t="n">
         <v>91974</v>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555453</v>
+        <v>555436</v>
       </c>
       <c r="R10" t="n">
-        <v>6943459</v>
+        <v>6943512</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135221221</v>
+        <v>135221211</v>
       </c>
       <c r="B11" t="n">
-        <v>91974</v>
+        <v>83222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,21 +1643,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555436</v>
+        <v>555442</v>
       </c>
       <c r="R11" t="n">
-        <v>6943512</v>
+        <v>6943498</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,32 +1739,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135221211</v>
+        <v>135221204</v>
       </c>
       <c r="B12" t="n">
-        <v>83222</v>
+        <v>92153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1774,13 +1774,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555442</v>
+        <v>555377</v>
       </c>
       <c r="R12" t="n">
-        <v>6943498</v>
+        <v>6943477</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,6 +1828,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1846,48 +1847,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135221204</v>
+        <v>104442994</v>
       </c>
       <c r="B13" t="n">
-        <v>92153</v>
+        <v>91966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>5321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öster-Skogsmyran, Mpd</t>
+          <t>Kullen, N om, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555377</v>
+        <v>555449</v>
       </c>
       <c r="R13" t="n">
-        <v>6943477</v>
+        <v>6943460</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1911,22 +1912,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,25 +1930,42 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>gammal grannaturskog i nordsluttning</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter # nerfallna grovgrenar av urgamla aspar</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104442994</v>
+        <v>135221208</v>
       </c>
       <c r="B14" t="n">
-        <v>91966</v>
+        <v>91937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,37 +1973,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5321</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kullen, N om, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555449</v>
+        <v>555391</v>
       </c>
       <c r="R14" t="n">
-        <v>6943460</v>
+        <v>6943515</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2019,12 +2027,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2033,68 +2051,50 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>gammal grannaturskog i nordsluttning</t>
-        </is>
-      </c>
-      <c r="AN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>1 substratenheter # nerfallna grovgrenar av urgamla aspar</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135221208</v>
+        <v>135221179</v>
       </c>
       <c r="B15" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555391</v>
+        <v>555255</v>
       </c>
       <c r="R15" t="n">
-        <v>6943515</v>
+        <v>6943525</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,7 +2176,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135221179</v>
+        <v>135221180</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555255</v>
+        <v>555233</v>
       </c>
       <c r="R16" t="n">
-        <v>6943525</v>
+        <v>6943506</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2283,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135221180</v>
+        <v>135221182</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555233</v>
+        <v>555232</v>
       </c>
       <c r="R17" t="n">
-        <v>6943506</v>
+        <v>6943486</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135221182</v>
+        <v>135221184</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555232</v>
+        <v>555255</v>
       </c>
       <c r="R18" t="n">
-        <v>6943486</v>
+        <v>6943491</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2497,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135221184</v>
+        <v>135221187</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555255</v>
+        <v>555287</v>
       </c>
       <c r="R19" t="n">
-        <v>6943491</v>
+        <v>6943497</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2604,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135221187</v>
+        <v>135221188</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555287</v>
+        <v>555291</v>
       </c>
       <c r="R20" t="n">
-        <v>6943497</v>
+        <v>6943507</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,7 +2711,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135221188</v>
+        <v>135221190</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555291</v>
+        <v>555276</v>
       </c>
       <c r="R21" t="n">
-        <v>6943507</v>
+        <v>6943511</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2818,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135221190</v>
+        <v>135221203</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555276</v>
+        <v>555366</v>
       </c>
       <c r="R22" t="n">
-        <v>6943511</v>
+        <v>6943491</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,7 +2925,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135221203</v>
+        <v>135221205</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555366</v>
+        <v>555382</v>
       </c>
       <c r="R23" t="n">
-        <v>6943491</v>
+        <v>6943480</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3032,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135221205</v>
+        <v>135221220</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555382</v>
+        <v>555445</v>
       </c>
       <c r="R24" t="n">
-        <v>6943480</v>
+        <v>6943509</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,7 +3139,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135221220</v>
+        <v>135221223</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555445</v>
+        <v>555413</v>
       </c>
       <c r="R25" t="n">
-        <v>6943509</v>
+        <v>6943520</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135221223</v>
+        <v>135221224</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555413</v>
+        <v>555371</v>
       </c>
       <c r="R26" t="n">
-        <v>6943520</v>
+        <v>6943530</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,7 +3353,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135221224</v>
+        <v>135221226</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555371</v>
+        <v>555352</v>
       </c>
       <c r="R27" t="n">
-        <v>6943530</v>
+        <v>6943528</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,48 +3460,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135221226</v>
+        <v>95981706</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öster-Skogsmyran, Mpd</t>
+          <t>Kullen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555352</v>
+        <v>555437</v>
       </c>
       <c r="R28" t="n">
-        <v>6943528</v>
+        <v>6943445</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3525,22 +3525,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,22 +3545,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95981706</v>
+        <v>135221207</v>
       </c>
       <c r="B29" t="n">
-        <v>83307</v>
+        <v>83358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,17 +3592,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kullen, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555437</v>
+        <v>555390</v>
       </c>
       <c r="R29" t="n">
-        <v>6943445</v>
+        <v>6943516</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3632,12 +3626,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3652,26 +3656,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135221207</v>
+        <v>135221192</v>
       </c>
       <c r="B30" t="n">
-        <v>83358</v>
+        <v>80488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,21 +3679,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555390</v>
+        <v>555299</v>
       </c>
       <c r="R30" t="n">
-        <v>6943516</v>
+        <v>6943491</v>
       </c>
       <c r="S30" t="n">
         <v>6</v>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3775,7 +3775,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135221192</v>
+        <v>135221197</v>
       </c>
       <c r="B31" t="n">
         <v>80488</v>
@@ -3810,13 +3810,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555299</v>
+        <v>555353</v>
       </c>
       <c r="R31" t="n">
-        <v>6943491</v>
+        <v>6943492</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3882,7 +3882,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135221197</v>
+        <v>135221200</v>
       </c>
       <c r="B32" t="n">
         <v>80488</v>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555353</v>
+        <v>555364</v>
       </c>
       <c r="R32" t="n">
-        <v>6943492</v>
+        <v>6943495</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3989,7 +3989,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135221200</v>
+        <v>135221217</v>
       </c>
       <c r="B33" t="n">
         <v>80488</v>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555364</v>
+        <v>555451</v>
       </c>
       <c r="R33" t="n">
-        <v>6943495</v>
+        <v>6943454</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4096,7 +4096,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135221217</v>
+        <v>135221219</v>
       </c>
       <c r="B34" t="n">
         <v>80488</v>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555451</v>
+        <v>555460</v>
       </c>
       <c r="R34" t="n">
-        <v>6943454</v>
+        <v>6943501</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4203,32 +4203,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135221219</v>
+        <v>135221189</v>
       </c>
       <c r="B35" t="n">
-        <v>80488</v>
+        <v>80492</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555460</v>
+        <v>555269</v>
       </c>
       <c r="R35" t="n">
-        <v>6943501</v>
+        <v>6943521</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4310,7 +4310,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135221189</v>
+        <v>135221193</v>
       </c>
       <c r="B36" t="n">
         <v>80492</v>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555269</v>
+        <v>555307</v>
       </c>
       <c r="R36" t="n">
-        <v>6943521</v>
+        <v>6943496</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4417,7 +4417,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135221193</v>
+        <v>135221225</v>
       </c>
       <c r="B37" t="n">
         <v>80492</v>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555307</v>
+        <v>555362</v>
       </c>
       <c r="R37" t="n">
-        <v>6943496</v>
+        <v>6943529</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4524,10 +4524,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135221225</v>
+        <v>135221201</v>
       </c>
       <c r="B38" t="n">
-        <v>80492</v>
+        <v>80493</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4535,21 +4535,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4559,10 +4559,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555362</v>
+        <v>555364</v>
       </c>
       <c r="R38" t="n">
-        <v>6943529</v>
+        <v>6943494</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4631,10 +4631,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135221201</v>
+        <v>135221198</v>
       </c>
       <c r="B39" t="n">
-        <v>80493</v>
+        <v>80499</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4642,21 +4642,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555364</v>
+        <v>555353</v>
       </c>
       <c r="R39" t="n">
-        <v>6943494</v>
+        <v>6943492</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4738,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135221198</v>
+        <v>135221185</v>
       </c>
       <c r="B40" t="n">
-        <v>80499</v>
+        <v>57972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4749,34 +4749,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555353</v>
+        <v>555257</v>
       </c>
       <c r="R40" t="n">
-        <v>6943492</v>
+        <v>6943491</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4808,7 +4820,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4818,7 +4830,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,27 +4857,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135221185</v>
+        <v>135221199</v>
       </c>
       <c r="B41" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4873,16 +4885,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4892,10 +4900,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555257</v>
+        <v>555363</v>
       </c>
       <c r="R41" t="n">
-        <v>6943491</v>
+        <v>6943498</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4927,7 +4935,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4937,7 +4945,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela stammen full.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4964,7 +4977,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135221199</v>
+        <v>135221209</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -4997,7 +5010,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5007,13 +5020,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555363</v>
+        <v>555410</v>
       </c>
       <c r="R42" t="n">
-        <v>6943498</v>
+        <v>6943513</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5042,7 +5055,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5052,12 +5065,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall. Hela stammen full.</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5084,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135221209</v>
+        <v>135221183</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5095,29 +5108,33 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5127,13 +5144,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555410</v>
+        <v>555234</v>
       </c>
       <c r="R43" t="n">
-        <v>6943513</v>
+        <v>6943495</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5162,7 +5179,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5172,12 +5189,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5204,44 +5216,44 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135221183</v>
+        <v>135221194</v>
       </c>
       <c r="B44" t="n">
-        <v>58136</v>
+        <v>58131</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5251,10 +5263,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555234</v>
+        <v>555330</v>
       </c>
       <c r="R44" t="n">
-        <v>6943495</v>
+        <v>6943504</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5286,7 +5298,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5296,7 +5308,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5323,60 +5335,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135221194</v>
+        <v>135221186</v>
       </c>
       <c r="B45" t="n">
-        <v>58131</v>
+        <v>79131</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103023</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555330</v>
+        <v>555278</v>
       </c>
       <c r="R45" t="n">
-        <v>6943504</v>
+        <v>6943488</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5442,48 +5442,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135221186</v>
+        <v>104442995</v>
       </c>
       <c r="B46" t="n">
-        <v>79131</v>
+        <v>80392</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öster-Skogsmyran, Mpd</t>
+          <t>Kullen, N om, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555278</v>
+        <v>555449</v>
       </c>
       <c r="R46" t="n">
-        <v>6943488</v>
+        <v>6943460</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5507,22 +5507,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5533,26 +5523,43 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>gammal grannaturskog i nordsluttning, mot sydvänd hyggeskant</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>2 substratenheter # urgamla aspar, uppskattningsvis runt 300 år, mycket grovbarkiga, 6 cm höga barkåsar</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104442995</v>
+        <v>135221196</v>
       </c>
       <c r="B47" t="n">
-        <v>80392</v>
+        <v>80438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5580,17 +5587,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kullen, N om, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555449</v>
+        <v>555341</v>
       </c>
       <c r="R47" t="n">
-        <v>6943460</v>
+        <v>6943495</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5614,12 +5621,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5630,40 +5647,23 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>gammal grannaturskog i nordsluttning, mot sydvänd hyggeskant</t>
-        </is>
-      </c>
-      <c r="AN47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>2 substratenheter # urgamla aspar, uppskattningsvis runt 300 år, mycket grovbarkiga, 6 cm höga barkåsar</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135221196</v>
+        <v>135221202</v>
       </c>
       <c r="B48" t="n">
         <v>80438</v>
@@ -5698,13 +5698,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555341</v>
+        <v>555364</v>
       </c>
       <c r="R48" t="n">
-        <v>6943495</v>
+        <v>6943494</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5770,7 +5770,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135221202</v>
+        <v>135221215</v>
       </c>
       <c r="B49" t="n">
         <v>80438</v>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555364</v>
+        <v>555450</v>
       </c>
       <c r="R49" t="n">
-        <v>6943494</v>
+        <v>6943462</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5877,7 +5877,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135221215</v>
+        <v>135221218</v>
       </c>
       <c r="B50" t="n">
         <v>80438</v>
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555450</v>
+        <v>555462</v>
       </c>
       <c r="R50" t="n">
-        <v>6943462</v>
+        <v>6943501</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5981,113 +5981,6 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>135221218</v>
-      </c>
-      <c r="B51" t="n">
-        <v>80438</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>229497</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Öster-Skogsmyran, Mpd</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>555462</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6943501</v>
-      </c>
-      <c r="S51" t="n">
-        <v>5</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Ånge</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Torp</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31212-2025 artfynd.xlsx
+++ b/artfynd/A 31212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221214</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221195</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981707</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221191</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221210</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221212</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221213</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221216</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221221</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221211</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221204</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1959,6 +2019,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104442994</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2066,6 +2131,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221208</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2173,6 +2243,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221179</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2280,6 +2355,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221180</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2387,6 +2467,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221182</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2494,6 +2579,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221184</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2601,6 +2691,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221187</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2708,6 +2803,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221188</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2815,6 +2915,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221190</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2922,6 +3027,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221203</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3029,6 +3139,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221205</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3136,6 +3251,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221220</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3243,6 +3363,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221223</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3350,6 +3475,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221224</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3457,6 +3587,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221226</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3558,6 +3693,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981706</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3665,6 +3805,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221207</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3772,6 +3917,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221192</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3879,6 +4029,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221197</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3986,6 +4141,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221200</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4093,6 +4253,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221217</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4200,6 +4365,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221219</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4307,6 +4477,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221189</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4414,6 +4589,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221193</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4521,6 +4701,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221225</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4628,6 +4813,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221201</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4735,6 +4925,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221198</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4854,6 +5049,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221185</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4974,6 +5174,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221199</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5094,6 +5299,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221209</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5213,6 +5423,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221183</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5332,6 +5547,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221194</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5439,6 +5659,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221186</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5553,6 +5778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104442995</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5660,6 +5890,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221196</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5767,6 +6002,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221202</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5874,6 +6114,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221215</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5981,8 +6226,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221218</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31212-2025 artfynd.xlsx
+++ b/artfynd/A 31212-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135221214</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135221195</v>
       </c>
       <c r="B3" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135221191</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135221210</v>
       </c>
       <c r="B6" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>135221212</v>
       </c>
       <c r="B7" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135221213</v>
       </c>
       <c r="B8" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135221216</v>
       </c>
       <c r="B9" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135221221</v>
       </c>
       <c r="B10" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>135221211</v>
       </c>
       <c r="B11" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>135221204</v>
       </c>
       <c r="B12" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>135221208</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>135221179</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>135221180</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>135221182</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135221184</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>135221187</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>135221188</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135221190</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>135221203</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135221205</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135221220</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>135221223</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135221224</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>135221226</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>135221207</v>
       </c>
       <c r="B29" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>135221192</v>
       </c>
       <c r="B30" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>135221197</v>
       </c>
       <c r="B31" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>135221200</v>
       </c>
       <c r="B32" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>135221217</v>
       </c>
       <c r="B33" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>135221219</v>
       </c>
       <c r="B34" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>135221189</v>
       </c>
       <c r="B35" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>135221193</v>
       </c>
       <c r="B36" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>135221225</v>
       </c>
       <c r="B37" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>135221201</v>
       </c>
       <c r="B38" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>135221198</v>
       </c>
       <c r="B39" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>135221185</v>
       </c>
       <c r="B40" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>135221199</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>135221209</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>135221183</v>
       </c>
       <c r="B43" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>135221194</v>
       </c>
       <c r="B44" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>135221186</v>
       </c>
       <c r="B45" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>135221196</v>
       </c>
       <c r="B47" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>135221202</v>
       </c>
       <c r="B48" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>135221215</v>
       </c>
       <c r="B49" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>135221218</v>
       </c>
       <c r="B50" t="n">
-        <v>80438</v>
+        <v>80476</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 31212-2025 artfynd.xlsx
+++ b/artfynd/A 31212-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135221214</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135221195</v>
       </c>
       <c r="B3" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135221191</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135221210</v>
       </c>
       <c r="B6" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>135221212</v>
       </c>
       <c r="B7" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135221213</v>
       </c>
       <c r="B8" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135221216</v>
       </c>
       <c r="B9" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135221221</v>
       </c>
       <c r="B10" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>135221211</v>
       </c>
       <c r="B11" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>135221204</v>
       </c>
       <c r="B12" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>135221208</v>
       </c>
       <c r="B14" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>135221179</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>135221180</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>135221182</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135221184</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>135221187</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>135221188</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>135221190</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>135221203</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>135221205</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135221220</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>135221223</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135221224</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>135221226</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>135221207</v>
       </c>
       <c r="B29" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>135221192</v>
       </c>
       <c r="B30" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>135221197</v>
       </c>
       <c r="B31" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>135221200</v>
       </c>
       <c r="B32" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>135221217</v>
       </c>
       <c r="B33" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>135221219</v>
       </c>
       <c r="B34" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>135221189</v>
       </c>
       <c r="B35" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>135221193</v>
       </c>
       <c r="B36" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>135221225</v>
       </c>
       <c r="B37" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>135221201</v>
       </c>
       <c r="B38" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>135221198</v>
       </c>
       <c r="B39" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>135221186</v>
       </c>
       <c r="B45" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>135221196</v>
       </c>
       <c r="B47" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>135221202</v>
       </c>
       <c r="B48" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>135221215</v>
       </c>
       <c r="B49" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>135221218</v>
       </c>
       <c r="B50" t="n">
-        <v>80476</v>
+        <v>80503</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 31212-2025 artfynd.xlsx
+++ b/artfynd/A 31212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95981707</v>
+        <v>135221214</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>97511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullen, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555429</v>
+        <v>555441</v>
       </c>
       <c r="R2" t="n">
-        <v>6943509</v>
+        <v>6943488</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,69 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95981707</t>
+          <t>https://artportalen.se/Sighting/135221214</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104442994</v>
+        <v>135221195</v>
       </c>
       <c r="B3" t="n">
-        <v>91966</v>
+        <v>91998</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5321</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullen, N om, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555449</v>
+        <v>555330</v>
       </c>
       <c r="R3" t="n">
-        <v>6943460</v>
+        <v>6943509</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,51 +881,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>gammal grannaturskog i nordsluttning</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # nerfallna grovgrenar av urgamla aspar</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104442994</t>
+          <t>https://artportalen.se/Sighting/135221195</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95981706</v>
+        <v>95981707</v>
       </c>
       <c r="B4" t="n">
-        <v>83307</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555437</v>
+        <v>555429</v>
       </c>
       <c r="R4" t="n">
-        <v>6943445</v>
+        <v>6943509</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1006,54 +1004,54 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95981706</t>
+          <t>https://artportalen.se/Sighting/95981707</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104442995</v>
+        <v>135221191</v>
       </c>
       <c r="B5" t="n">
-        <v>80392</v>
+        <v>92048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kullen, N om, Mpd</t>
+          <t>Öster-Skogsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555449</v>
+        <v>555298</v>
       </c>
       <c r="R5" t="n">
-        <v>6943460</v>
+        <v>6943497</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,12 +1075,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,39 +1101,5134 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>gammal grannaturskog i nordsluttning, mot sydvänd hyggeskant</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>2 substratenheter # urgamla aspar, uppskattningsvis runt 300 år, mycket grovbarkiga, 6 cm höga barkåsar</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221191</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135221210</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>555424</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6943510</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221210</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135221212</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>555436</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6943491</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221212</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135221213</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>555423</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6943489</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221213</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135221216</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>555453</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6943459</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221216</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135221221</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>555436</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6943512</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221221</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135221211</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>555442</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6943498</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221211</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135221204</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>555377</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6943477</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221204</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104442994</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91966</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kullen, N om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>555449</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6943460</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>gammal grannaturskog i nordsluttning</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter # nerfallna grovgrenar av urgamla aspar</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104442994</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135221208</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>555391</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6943515</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221208</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135221179</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>555255</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6943525</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221179</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135221180</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>555233</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6943506</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221180</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135221182</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>555232</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6943486</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221182</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135221184</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>555255</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6943491</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221184</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135221187</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>555287</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6943497</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221187</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135221188</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>555291</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6943507</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221188</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135221190</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>555276</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6943511</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221190</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135221203</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>555366</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6943491</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221203</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135221205</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>555382</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6943480</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221205</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135221220</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>555445</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6943509</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221220</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135221223</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>555413</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6943520</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221223</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135221224</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>555371</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6943530</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221224</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135221226</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>555352</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6943528</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221226</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>95981706</v>
+      </c>
+      <c r="B28" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kullen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>555437</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6943445</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981706</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135221207</v>
+      </c>
+      <c r="B29" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>555390</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6943516</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221207</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135221192</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>555299</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6943491</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221192</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135221197</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>555353</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6943492</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221197</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135221200</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>555364</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6943495</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221200</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135221217</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>555451</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6943454</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221217</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135221219</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>555460</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6943501</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221219</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135221189</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>555269</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6943521</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221189</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135221193</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>555307</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6943496</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221193</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135221225</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>555362</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6943529</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221225</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135221201</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>555364</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6943494</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221201</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135221198</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80567</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>555353</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6943492</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221198</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135221185</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>555257</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6943491</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221185</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135221199</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>555363</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6943498</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Hela stammen full.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221199</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135221209</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>555410</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6943513</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221209</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135221183</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>555234</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6943495</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221183</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135221194</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>555330</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6943504</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221194</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135221186</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>555278</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6943488</v>
+      </c>
+      <c r="S45" t="n">
+        <v>7</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221186</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>104442995</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kullen, N om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>555449</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6943460</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>gammal grannaturskog i nordsluttning, mot sydvänd hyggeskant</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>2 substratenheter # urgamla aspar, uppskattningsvis runt 300 år, mycket grovbarkiga, 6 cm höga barkåsar</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104442995</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135221196</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80506</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>555341</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6943495</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221196</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135221202</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80506</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>555364</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6943494</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221202</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135221215</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80506</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>555450</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6943462</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221215</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135221218</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80506</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Öster-Skogsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>555462</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6943501</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135221218</t>
         </is>
       </c>
     </row>
@@ -1135,6 +6238,51 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31212-2025 artfynd.xlsx
+++ b/artfynd/A 31212-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135221214</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135221195</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135221191</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135221210</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>135221212</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135221213</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135221216</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135221221</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>135221204</v>
       </c>
       <c r="B12" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>135221208</v>
       </c>
       <c r="B14" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
